--- a/business_surveys/042_property_value_perception_survey--business_surveys.xlsx
+++ b/business_surveys/042_property_value_perception_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,46 +515,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>property_visit_frequency</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Property Value Perception Survey</t>
+          <t>How often do you visit this area?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>page_one</t>
+          <t>property_type</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>How often do you visit this area?</t>
+          <t>Property Type</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +566,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>page_one_label</t>
+          <t>public_transportation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Property Type</t>
+          <t>How would you rate the quality of local public transportation?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>area_features</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>What do you like least about this area?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>page_two</t>
+          <t>valued_features</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>What do you like least about this area?</t>
+          <t>What features do you value most in a property?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,179 +635,156 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>page_two_label</t>
+          <t>desired_amenities</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Area Features</t>
+          <t>What amenities would you like to see in this area?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>area_safety</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How would you rate the overall safety of this area?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>amenities_quality</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How would you rate the overall quality of local amenities in this area?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>parking_importance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How important is the availability of parking to you in this area?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>business_quality</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How would you rate the overall quality of local businesses in this area?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>developments_frequency</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How often do you think new developments/changes should be made in this area?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>sense_of_community</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>How would you rate the overall sense of community in this area?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>form_description</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -822,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
@@ -850,75 +827,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>page_one_choices</t>
+          <t>property_visit_frequency_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>residential</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Residential</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>page_one_choices</t>
+          <t>property_visit_frequency_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>commercial</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>page_one_choices</t>
+          <t>property_visit_frequency_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>recreational</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Recreational</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>page_one_choices</t>
+          <t>property_visit_frequency_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>page_one_label_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -935,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>page_one_label_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>page_one_label_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -969,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>page_one_label_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -986,68 +963,680 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>page_two_label_choices</t>
+          <t>public_transportation_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>parks</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Parks</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>page_two_label_choices</t>
+          <t>public_transportation_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>public_transportation</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Public transportation</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>page_two_label_choices</t>
+          <t>public_transportation_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>schools</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Schools</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>page_two_label_choices</t>
+          <t>public_transportation_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>valued_features_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>parks</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Parks</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>valued_features_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>public_transportation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Public transportation</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>valued_features_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>schools</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>valued_features_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>shopping</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Shopping</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>valued_features_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>safety</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>valued_features_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>proximity_to_work</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Proximity to work</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>desired_amenities_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>parks</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Parks</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>desired_amenities_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>public_transportation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Public transportation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>desired_amenities_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>schools</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Schools</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>desired_amenities_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>shopping</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>desired_amenities_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>restaurants</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Restaurants</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>desired_amenities_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>gyms</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Gyms</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>area_safety_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>area_safety_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>area_safety_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>area_safety_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>amenities_quality_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>amenities_quality_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>amenities_quality_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>amenities_quality_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>parking_importance_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>very_important</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Very important</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>parking_importance_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>somewhat_important</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Somewhat important</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>parking_importance_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>not_very_important</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Not very important</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>parking_importance_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>not_at_all_important</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Not at all important</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>business_quality_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>business_quality_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>business_quality_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>business_quality_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>developments_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>frequently</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Frequently</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>developments_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>occasionally</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Occasionally</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>developments_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>developments_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>never</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sense_of_community_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sense_of_community_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sense_of_community_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sense_of_community_choices</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Poor</t>
         </is>
       </c>
     </row>
